--- a/Digital-Business-Toolkit/11-Business-Control-Center/Product.xlsx
+++ b/Digital-Business-Toolkit/11-Business-Control-Center/Product.xlsx
@@ -851,7 +851,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — כל העסק שלכם, במבט אחד</t>
+          <t>JobMargin — כל העסק שלכם, במבט אחד</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -1110,7 +1110,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>שורה אחת לכל פרויקט — שם הפרויקט חייב להיות זהה למה שהוזן בכל שאר מוצרי ContractorOS</t>
+          <t>שורה אחת לכל פרויקט — שם הפרויקט חייב להיות זהה למה שהוזן בכל שאר מוצרי JobMargin</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="C4" s="35" t="inlineStr">
         <is>
-          <t>מערכת הניהול המרכזית של ContractorOS — מאחדת תמונת מצב מכל 10 המוצרים (תמחור, תקציב, הצעות מחיר, גבייה, תזרים, שעות עבודה, לידים, מלאי, תוספות, ביצוע) ללוח בקרה עסקי אחד.</t>
+          <t>מערכת הניהול המרכזית של JobMargin — מאחדת תמונת מצב מכל 10 המוצרים (תמחור, תקציב, הצעות מחיר, גבייה, תזרים, שעות עבודה, לידים, מלאי, תוספות, ביצוע) ללוח בקרה עסקי אחד.</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="C5" s="35" t="inlineStr">
         <is>
-          <t>בעלי עסק שכבר עובדים (או רוצים להתחיל לעבוד) עם כמה מוצרי ContractorOS ורוצים תמונת על אחת, בלי לקפוץ בין קבצים.</t>
+          <t>בעלי עסק שכבר עובדים (או רוצים להתחיל לעבוד) עם כמה מוצרי JobMargin ורוצים תמונת על אחת, בלי לקפוץ בין קבצים.</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>לפי שם הפרויקט בלבד — אין מספור נפרד. הקפידו להשתמש באותו שם פרויקט בדיוק בכל מוצר ContractorOS שבו אתם עובדים, כדי שהמערכת המרכזית תשקף נכון.</t>
+          <t>לפי שם הפרויקט בלבד — אין מספור נפרד. הקפידו להשתמש באותו שם פרויקט בדיוק בכל מוצר JobMargin שבו אתם עובדים, כדי שהמערכת המרכזית תשקף נכון.</t>
         </is>
       </c>
     </row>
